--- a/Cechy/Nadgodziny nowe - scenariusze testowe.xlsx
+++ b/Cechy/Nadgodziny nowe - scenariusze testowe.xlsx
@@ -7,14 +7,16 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Scenariusze" sheetId="1" r:id="rId1"/>
     <sheet name="Srodowisko i jak sprawdzic" sheetId="2" r:id="rId2"/>
+    <sheet name="Rownowazny 4msc" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Scenariusze!$A$1:$L$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rownowazny 4msc'!$A$1:$M$9</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
@@ -294,6 +296,192 @@
   </si>
   <si>
     <t>Patrz wiersz NG-08 (podswietlony) w arkuszu Scenariusze - dzien "Pracy w swiete" bez flagi NadgodzinySW powoduje, ze wszystkie 4 nowe cechy zwracaja 0 dla strefy poza norma.</t>
+  </si>
+  <si>
+    <t>Arkusz "Rownowazny 4msc"</t>
+  </si>
+  <si>
+    <t>Pracownicy RC-01..RC-08, kalendarz JUZ ISTNIEJACY w bazie "4msc" (Kalendarze.ID=24, AlgorytmDobowa=RownowaznyCzasPracy - norma dobowa = MAX(plan dnia, Etat.NormaDobowa=8:00), NIE tworzony/modyfikowany przez te pliki). Ten kalendarz jest juz uzywany przez demo-pracownika "0001" - nie ruszany.</t>
+  </si>
+  <si>
+    <t>Plan dnia (Od-Czas)</t>
+  </si>
+  <si>
+    <t>Praca rzeczywista (Od-Czas)</t>
+  </si>
+  <si>
+    <t>Norma dobowa (rownowazna)</t>
+  </si>
+  <si>
+    <t>Strefa "poza norma" (Od-Czas)</t>
+  </si>
+  <si>
+    <t>Nadgodziny NSW nowe</t>
+  </si>
+  <si>
+    <t>RC-01</t>
+  </si>
+  <si>
+    <t>Kamiński Bartosz</t>
+  </si>
+  <si>
+    <t>2026-11-10</t>
+  </si>
+  <si>
+    <t>Plan 8h (zwykly dzien), praca dokladnie 8h - baseline</t>
+  </si>
+  <si>
+    <t>8:00-16:00 (8:00)</t>
+  </si>
+  <si>
+    <t>max(8:00,8:00)=8:00</t>
+  </si>
+  <si>
+    <t>brak (worked=plan)</t>
+  </si>
+  <si>
+    <t>Praca=plan=8h -&gt; caly dzien w normie, zadnej strefy poza norma. Potwierdza, ze RownowaznyCzasPracy daje ten sam wynik co Konfiguracja, gdy plan=norma etatu</t>
+  </si>
+  <si>
+    <t>RC-02</t>
+  </si>
+  <si>
+    <t>Adamska Paulina</t>
+  </si>
+  <si>
+    <t>2026-11-11</t>
+  </si>
+  <si>
+    <t>Plan 8h, praca 10h -&gt; nadgodziny dobowe</t>
+  </si>
+  <si>
+    <t>8:00-18:00 (10:00)</t>
+  </si>
+  <si>
+    <t>16:00-18:00 (2:00)</t>
+  </si>
+  <si>
+    <t>Ta sama logika co kalendarz Standard (plan=norma=8h) - 2h ponad norme, w calosci dzienne -&gt; 50%</t>
+  </si>
+  <si>
+    <t>RC-03</t>
+  </si>
+  <si>
+    <t>Wilk Damian</t>
+  </si>
+  <si>
+    <t>2026-11-12</t>
+  </si>
+  <si>
+    <t>Plan 10h (wydluzony dzien rownowazny), praca dokladnie 10h</t>
+  </si>
+  <si>
+    <t>6:00-16:00 (10:00)</t>
+  </si>
+  <si>
+    <t>max(10:00,8:00)=10:00</t>
+  </si>
+  <si>
+    <t>KLUCZOWY test rownowaznego czasu pracy: 10h pracy, ZERO nadgodzin, bo plan(10h)&gt;etat(8h) wiec norma=10h=praca. Na kalendarzu Standard te same 10h dalyby 2h nadgodzin</t>
+  </si>
+  <si>
+    <t>RC-04</t>
+  </si>
+  <si>
+    <t>Górska Natalia</t>
+  </si>
+  <si>
+    <t>2026-11-13</t>
+  </si>
+  <si>
+    <t>Plan 10h, praca 12h -&gt; nadgodziny ponad wydluzony dzien</t>
+  </si>
+  <si>
+    <t>6:00-18:00 (12:00)</t>
+  </si>
+  <si>
+    <t>Norma=10h (plan wygrywa, bo dluzszy niz etat). 2h ponad 10h -&gt; 50% dzienne</t>
+  </si>
+  <si>
+    <t>RC-05</t>
+  </si>
+  <si>
+    <t>Sikora Michał</t>
+  </si>
+  <si>
+    <t>2026-11-14</t>
+  </si>
+  <si>
+    <t>Plan 12h (maksymalny dzien rownowazny), praca dokladnie 12h</t>
+  </si>
+  <si>
+    <t>max(12:00,8:00)=12:00</t>
+  </si>
+  <si>
+    <t>Jak RC-03, ale przy maksymalnym dopuszczalnym wydluzeniu dnia (12h) - ZERO nadgodzin za 12h pracy, gdy tyle wlasnie zaplanowano</t>
+  </si>
+  <si>
+    <t>RC-06</t>
+  </si>
+  <si>
+    <t>Kowalczyk Magdalena</t>
+  </si>
+  <si>
+    <t>2026-11-15</t>
+  </si>
+  <si>
+    <t>Plan 12h, praca 14h -&gt; nadgodziny ponad maksymalny dzien</t>
+  </si>
+  <si>
+    <t>6:00-20:00 (14:00)</t>
+  </si>
+  <si>
+    <t>18:00-20:00 (2:00)</t>
+  </si>
+  <si>
+    <t>Norma=12h. 2h ponad 12h -&gt; 50% dzienne</t>
+  </si>
+  <si>
+    <t>RC-07</t>
+  </si>
+  <si>
+    <t>Jankowski Paweł</t>
+  </si>
+  <si>
+    <t>2026-11-16</t>
+  </si>
+  <si>
+    <t>Plan 4h (dzien kompensacyjny/krotki), praca do 8h</t>
+  </si>
+  <si>
+    <t>8:00-12:00 (4:00)</t>
+  </si>
+  <si>
+    <t>max(4:00,8:00)=8:00</t>
+  </si>
+  <si>
+    <t>12:00-16:00 (4:00)</t>
+  </si>
+  <si>
+    <t>"Podloga" etatu (8h) wygrywa nad krotkim planem (4h) -&gt; norma=8h. Cale 4h ponad plan miesci sie w oknie (plan,norma]=(4h,8h] -&gt; okresowe, NIE dobowe 50% (bo praca konczy sie dokladnie na normie)</t>
+  </si>
+  <si>
+    <t>RC-08</t>
+  </si>
+  <si>
+    <t>Mazur Weronika</t>
+  </si>
+  <si>
+    <t>2026-11-17</t>
+  </si>
+  <si>
+    <t>Plan 4h, praca 10h -&gt; okresowe + dobowe w jednej strefie</t>
+  </si>
+  <si>
+    <t>12:00-18:00 (6:00)</t>
+  </si>
+  <si>
+    <t>Pierwsze 4h strefy (12:00-16:00) w oknie (plan,norma]=(4h,8h] -&gt; okresowe=4:00. Kolejne 2h (16:00-18:00) ponad norme(8h) -&gt; 50%=2:00. Test rozbicia jednej strefy na okresowe+dobowe</t>
   </si>
 </sst>
 </file>
@@ -1138,6 +1326,407 @@
         <v>90</v>
       </c>
     </row>
+    <row r="10" ht="7.2" customHeight="1">
+      <c r="A10" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.710938" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="30.710938" customWidth="1"/>
+    <col min="5" max="5" width="18.710938" customWidth="1"/>
+    <col min="6" max="6" width="18.710938" customWidth="1"/>
+    <col min="7" max="7" width="20.710938" customWidth="1"/>
+    <col min="8" max="8" width="18.710938" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="50.710938" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="8.16" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" ht="45">
+      <c r="A2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" ht="30">
+      <c r="A3" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" ht="60">
+      <c r="A4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" ht="30">
+      <c r="A5" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" ht="45">
+      <c r="A6" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" ht="30">
+      <c r="A7" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" ht="60">
+      <c r="A8" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" ht="60">
+      <c r="A9" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M9"/>
+</worksheet>
 </file>
--- a/Cechy/Nadgodziny nowe - scenariusze testowe.xlsx
+++ b/Cechy/Nadgodziny nowe - scenariusze testowe.xlsx
@@ -7,16 +7,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Scenariusze" sheetId="1" r:id="rId1"/>
     <sheet name="Srodowisko i jak sprawdzic" sheetId="2" r:id="rId2"/>
     <sheet name="Rownowazny 4msc" sheetId="3" r:id="rId3"/>
+    <sheet name="Lider zmiany" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Scenariusze!$A$1:$L$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rownowazny 4msc'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Lider zmiany'!$A$1:$L$5</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
@@ -304,6 +306,12 @@
     <t>Pracownicy RC-01..RC-08, kalendarz JUZ ISTNIEJACY w bazie "4msc" (Kalendarze.ID=24, AlgorytmDobowa=RownowaznyCzasPracy - norma dobowa = MAX(plan dnia, Etat.NormaDobowa=8:00), NIE tworzony/modyfikowany przez te pliki). Ten kalendarz jest juz uzywany przez demo-pracownika "0001" - nie ruszany.</t>
   </si>
   <si>
+    <t>Arkusz "Lider zmiany"</t>
+  </si>
+  <si>
+    <t>Pracownicy LZ-01..LZ-04, powtorzenie NG-01/NG-02/RC-02/RC-04 z dopisana strefa "Lider zmiany" (DefinicjeStref ID=25) na cala dlugosc zmiany - test, ze jej obecnosc NIE zmienia wyniku 4 cech na strefie "Praca poza norma". [0:00] w kolumnie Strefy = brak &lt;OdGodziny&gt; w XML zapisal sie jako 0:00, nie jako Time.Empty tak jak w danych zastanych dla pracownika "0001" - patrz komentarz w pliku 03.</t>
+  </si>
+  <si>
     <t>Plan dnia (Od-Czas)</t>
   </si>
   <si>
@@ -482,6 +490,93 @@
   </si>
   <si>
     <t>Pierwsze 4h strefy (12:00-16:00) w oknie (plan,norma]=(4h,8h] -&gt; okresowe=4:00. Kolejne 2h (16:00-18:00) ponad norme(8h) -&gt; 50%=2:00. Test rozbicia jednej strefy na okresowe+dobowe</t>
+  </si>
+  <si>
+    <t>Kalendarz</t>
+  </si>
+  <si>
+    <t>Odpowiednik scenariusza</t>
+  </si>
+  <si>
+    <t>Plan / praca rzeczywista</t>
+  </si>
+  <si>
+    <t>Strefy dnia</t>
+  </si>
+  <si>
+    <t>LZ-01</t>
+  </si>
+  <si>
+    <t>Zieliński Kacper</t>
+  </si>
+  <si>
+    <t>Test nadgodziny nowe (Standard)</t>
+  </si>
+  <si>
+    <t>2026-11-18</t>
+  </si>
+  <si>
+    <t>Plan 8:00-16:00 (8:00) / praca 8:00-18:00 (10:00)</t>
+  </si>
+  <si>
+    <t>Praca w normie 8:00-16:00 (8:00); Praca poza normą 16:00-18:00 (2:00); Lider zmiany [0:00]-8:00 (8:00, cała zmiana)</t>
+  </si>
+  <si>
+    <t>Musi wyjść identycznie jak NG-01 (2:00/0/0/0) - obecność strefy Lider zmiany (poza chronologicznym sumowaniem "w normie"+"poza normą") nie może zmienić wyniku</t>
+  </si>
+  <si>
+    <t>LZ-02</t>
+  </si>
+  <si>
+    <t>Wróblewska Marta</t>
+  </si>
+  <si>
+    <t>2026-11-19</t>
+  </si>
+  <si>
+    <t>Plan 14:00-22:00 (8:00) / praca 14:00-24:00 (10:00)</t>
+  </si>
+  <si>
+    <t>Praca w normie 14:00-22:00 (8:00); Praca poza normą 22:00-24:00 (2:00, w oknie nocnym); Lider zmiany [0:00]-8:00 (8:00)</t>
+  </si>
+  <si>
+    <t>Musi wyjść identycznie jak NG-02 (0/2:00/0/0) - test że strefa Lider zmiany nie zaburza też przeniesienia godzin nocnych do 100%</t>
+  </si>
+  <si>
+    <t>LZ-03</t>
+  </si>
+  <si>
+    <t>Kaczor Bartłomiej</t>
+  </si>
+  <si>
+    <t>4msc (równoważny czas pracy)</t>
+  </si>
+  <si>
+    <t>2026-11-20</t>
+  </si>
+  <si>
+    <t>Praca w normie 8:00-16:00 (8:00); Praca poza normą 16:00-18:00 (2:00); Lider zmiany [0:00]-8:00 (8:00)</t>
+  </si>
+  <si>
+    <t>Musi wyjść identycznie jak RC-02 - test na kalendarzu RÓWNOWAŻNYM (AlgorytmDobowa=RównoważnyCzasPracy), nie tylko Standard</t>
+  </si>
+  <si>
+    <t>LZ-04</t>
+  </si>
+  <si>
+    <t>Sadowska Klaudia</t>
+  </si>
+  <si>
+    <t>2026-11-21</t>
+  </si>
+  <si>
+    <t>Plan 6:00-16:00 (10:00, wydłużony dzień) / praca 6:00-18:00 (12:00)</t>
+  </si>
+  <si>
+    <t>Praca w normie 6:00-16:00 (10:00); Praca poza normą 16:00-18:00 (2:00); Lider zmiany [0:00]-10:00 (10:00, cała wydłużona zmiana)</t>
+  </si>
+  <si>
+    <t>Musi wyjść identycznie jak RC-04 (norma=plan=10:00, bo wydłużony dzień &gt; 8h etatu) - test kombinacji Lider zmiany + norma równoważna dłuższa niż 8h</t>
   </si>
 </sst>
 </file>
@@ -1334,6 +1429,14 @@
         <v>92</v>
       </c>
     </row>
+    <row r="11" ht="7.2" customHeight="1">
+      <c r="A11" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1371,16 +1474,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>
@@ -1392,7 +1495,7 @@
         <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>10</v>
@@ -1400,28 +1503,28 @@
     </row>
     <row r="2" ht="45">
       <c r="A2" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>19</v>
@@ -1436,33 +1539,33 @@
         <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" ht="30">
       <c r="A3" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>18</v>
@@ -1477,33 +1580,33 @@
         <v>19</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" ht="60">
       <c r="A4" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>19</v>
@@ -1518,33 +1621,33 @@
         <v>19</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" ht="30">
       <c r="A5" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>18</v>
@@ -1559,33 +1662,33 @@
         <v>19</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" ht="45">
       <c r="A6" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>19</v>
@@ -1600,33 +1703,33 @@
         <v>19</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" ht="30">
       <c r="A7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>18</v>
@@ -1641,33 +1744,33 @@
         <v>19</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" ht="60">
       <c r="A8" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>19</v>
@@ -1682,33 +1785,33 @@
         <v>19</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" ht="60">
       <c r="A9" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>18</v>
@@ -1723,10 +1826,223 @@
         <v>19</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M9"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.710938" customWidth="1"/>
+    <col min="3" max="3" width="22.710938" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="32.710938" customWidth="1"/>
+    <col min="7" max="7" width="45.710938" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="50.710938" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="8.16" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" ht="60">
+      <c r="A2" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" ht="45">
+      <c r="A3" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" ht="60">
+      <c r="A4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" ht="45">
+      <c r="A5" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L5"/>
+</worksheet>
 </file>
--- a/Cechy/Nadgodziny nowe - scenariusze testowe.xlsx
+++ b/Cechy/Nadgodziny nowe - scenariusze testowe.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Scenariusze!$A$1:$L$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rownowazny 4msc'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rownowazny 4msc'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Lider zmiany'!$A$1:$L$5</definedName>
   </definedNames>
   <calcPr/>
@@ -39,9 +39,6 @@
     <t>Opis scenariusza</t>
   </si>
   <si>
-    <t>Kalendarz (wzorzec)</t>
-  </si>
-  <si>
     <t>Plan dnia (Definicja / Od-Czas)</t>
   </si>
   <si>
@@ -57,6 +54,9 @@
     <t>Nadgodziny okresowe nowe</t>
   </si>
   <si>
+    <t>Nadgodziny NSW nowe</t>
+  </si>
+  <si>
     <t>Uwagi / co sprawdza</t>
   </si>
   <si>
@@ -324,9 +324,6 @@
     <t>Strefa "poza norma" (Od-Czas)</t>
   </si>
   <si>
-    <t>Nadgodziny NSW nowe</t>
-  </si>
-  <si>
     <t>RC-01</t>
   </si>
   <si>
@@ -490,6 +487,30 @@
   </si>
   <si>
     <t>Pierwsze 4h strefy (12:00-16:00) w oknie (plan,norma]=(4h,8h] -&gt; okresowe=4:00. Kolejne 2h (16:00-18:00) ponad norme(8h) -&gt; 50%=2:00. Test rozbicia jednej strefy na okresowe+dobowe</t>
+  </si>
+  <si>
+    <t>RC-09</t>
+  </si>
+  <si>
+    <t>Wysocka Aleksandra</t>
+  </si>
+  <si>
+    <t>2026-11-22</t>
+  </si>
+  <si>
+    <t>Dzien Swieto (NadgodzinySW=1) na kalendarzu ROWNOWAZNYM, praca bez planu</t>
+  </si>
+  <si>
+    <t>brak planu (0:00)</t>
+  </si>
+  <si>
+    <t>9:00-13:00 (4:00)</t>
+  </si>
+  <si>
+    <t>nie dotyczy (dzien wykluczony z algorytmu dobowego)</t>
+  </si>
+  <si>
+    <t>Odpowiednik NG-07, ale na kalendarzu rownowaznym 4msc - test ze NSW nowe NIE zalezy od AlgorytmDobowa (Konfiguracja vs RownowaznyCzasPracy). Wynik musi byc identyczny jak NG-07 (NSW=4:00)</t>
   </si>
   <si>
     <t>Kalendarz</t>
@@ -1486,16 +1507,16 @@
         <v>98</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>10</v>
@@ -1503,69 +1524,69 @@
     </row>
     <row r="2" ht="45">
       <c r="A2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="3" ht="30">
       <c r="A3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>18</v>
@@ -1580,74 +1601,74 @@
         <v>19</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" ht="60">
       <c r="A4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="5" ht="30">
       <c r="A5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>18</v>
@@ -1662,74 +1683,74 @@
         <v>19</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" ht="45">
       <c r="A6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="7" ht="30">
       <c r="A7" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>18</v>
@@ -1744,33 +1765,33 @@
         <v>19</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" ht="60">
       <c r="A8" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>19</v>
@@ -1785,33 +1806,33 @@
         <v>19</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" ht="60">
       <c r="A9" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>18</v>
@@ -1826,11 +1847,52 @@
         <v>19</v>
       </c>
       <c r="M9" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" ht="75">
+      <c r="A10" s="2" t="s">
         <v>154</v>
       </c>
+      <c r="B10" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>161</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:M10"/>
 </worksheet>
 </file>
 
@@ -1860,31 +1922,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>10</v>
@@ -1892,25 +1954,25 @@
     </row>
     <row r="2" ht="60">
       <c r="A2" s="2" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>18</v>
@@ -1925,30 +1987,30 @@
         <v>19</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" ht="45">
       <c r="A3" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>19</v>
@@ -1963,30 +2025,30 @@
         <v>19</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" ht="60">
       <c r="A4" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>18</v>
@@ -2001,30 +2063,30 @@
         <v>19</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" ht="45">
       <c r="A5" s="2" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>18</v>
@@ -2039,7 +2101,7 @@
         <v>19</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
